--- a/S2 CP/ClinicalExam/CE_CP_T0.xlsx
+++ b/S2 CP/ClinicalExam/CE_CP_T0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GBW_MyPrograms\PredSim-workshop-smalll-2025\S2 CP\ClinicalExam\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GBW_MyPrograms\PredSim-workshop-ESMAC-2026\S2 CP\ClinicalExam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8843E397-2369-4BCE-B65D-09A8575AF5DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F406033-59E4-4CB8-AA80-ED86A134BFFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -46,9 +46,6 @@
   </si>
   <si>
     <t>pROM_Ankledf90_L</t>
-  </si>
-  <si>
-    <t>CP_SMALLL</t>
   </si>
   <si>
     <t>pROM_Poplbi_R</t>
@@ -139,6 +136,9 @@
   </si>
   <si>
     <t>Step 4</t>
+  </si>
+  <si>
+    <t>CP_ESMAC</t>
   </si>
 </sst>
 </file>
@@ -553,10 +553,10 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>3</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -564,12 +564,12 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B4" s="12"/>
       <c r="G4" s="1"/>
@@ -579,13 +579,13 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" s="10">
         <v>3</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="4"/>
@@ -594,7 +594,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" s="10">
         <v>3</v>
@@ -606,7 +606,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" s="10">
         <v>5</v>
@@ -618,7 +618,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" s="10">
         <v>5</v>
@@ -630,7 +630,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" s="3">
         <v>3</v>
@@ -642,7 +642,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10" s="3">
         <v>3</v>
@@ -654,7 +654,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11" s="3">
         <v>4</v>
@@ -666,7 +666,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12" s="3">
         <v>5</v>
@@ -678,7 +678,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13" s="10">
         <v>3</v>
@@ -690,7 +690,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" s="10">
         <v>4</v>
@@ -700,7 +700,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" s="10">
         <v>3</v>
@@ -710,7 +710,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B16" s="10">
         <v>3</v>
@@ -719,7 +719,7 @@
     <row r="17" spans="1:16384" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:16384" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="6"/>
@@ -17107,13 +17107,13 @@
     </row>
     <row r="19" spans="1:16384" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B19" s="12"/>
     </row>
     <row r="20" spans="1:16384" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B20" s="3">
         <v>-70</v>
@@ -17129,7 +17129,7 @@
     </row>
     <row r="22" spans="1:16384" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22" s="10">
         <v>15</v>
@@ -17137,7 +17137,7 @@
     </row>
     <row r="23" spans="1:16384" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" s="10">
         <v>10</v>
@@ -17161,13 +17161,13 @@
     </row>
     <row r="26" spans="1:16384" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26" s="12"/>
     </row>
     <row r="27" spans="1:16384" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B27" s="3">
         <v>-80</v>
@@ -17177,7 +17177,7 @@
     </row>
     <row r="28" spans="1:16384" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B28" s="3">
         <v>-65</v>
@@ -17187,7 +17187,7 @@
     </row>
     <row r="29" spans="1:16384" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B29" s="12"/>
       <c r="E29" s="1"/>
@@ -17195,7 +17195,7 @@
     </row>
     <row r="30" spans="1:16384" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B30" s="3">
         <v>-10</v>
@@ -17205,7 +17205,7 @@
     </row>
     <row r="31" spans="1:16384" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B31" s="3">
         <v>-10</v>
@@ -17215,20 +17215,20 @@
     </row>
     <row r="32" spans="1:16384" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="4"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E33" s="1"/>
       <c r="F33" s="4"/>
